--- a/static/uploads/mau/hopdong/nt1/duoi_o2/hdnh.xlsx
+++ b/static/uploads/mau/hopdong/nt1/duoi_o2/hdnh.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DAT\Desktop\code\working\HRM\static\uploads\mau\hopdong\nt1\duoi_o2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DTD\Code\HRM\static\uploads\mau\hopdong\nt1\duoi_o2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39B13E42-3FE8-40ED-BEA3-52A19E89B2A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD5DA888-F361-4F29-A065-63CE2E6F6E92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="20640" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MẪU IN HỢP ĐỒNG LAO ĐỘNG" sheetId="2" r:id="rId1"/>
@@ -457,14 +457,14 @@
     <t>Không</t>
   </si>
   <si>
-    <t>Địa chỉ: TDP 7 - Thuỷ Đường - Thuỷ Nguyên - Hải Phòng
+    <t>- Địa điểm làm việc: + Tổ dân phố 7, Phường Thủy Nguyên, TP Hải Phòng</t>
+  </si>
+  <si>
+    <t>Tổ dân phố 7, Phường Thủy Nguyên, TP Hải Phòng</t>
+  </si>
+  <si>
+    <t>Địa chỉ: TDP 7 - Thuỷ Nguyên - Hải Phòng
 ĐT: 02253.642.408</t>
-  </si>
-  <si>
-    <t>Tổ dân phố 7, Phường Thủy Đường, TP Thủy Nguyên, TP Hải Phòng</t>
-  </si>
-  <si>
-    <t>- Địa điểm làm việc: + Tổ dân phố 7, Phường Thủy Đường, TP Thủy Nguyên, TP Hải Phòng</t>
   </si>
 </sst>
 </file>
@@ -1122,16 +1122,16 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:X127"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="8" width="4" customWidth="1"/>
     <col min="9" max="10" width="8" customWidth="1"/>
     <col min="11" max="12" width="3" customWidth="1"/>
     <col min="13" max="23" width="4" customWidth="1"/>
-    <col min="24" max="24" width="6.5703125" customWidth="1"/>
+    <col min="24" max="24" width="6.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4"/>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -1161,13 +1161,13 @@
       <c r="W1" s="5"/>
       <c r="X1" s="5"/>
     </row>
-    <row r="2" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4"/>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
       <c r="E2" s="6" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F2" s="7"/>
       <c r="G2" s="7"/>
@@ -1191,7 +1191,7 @@
       <c r="W2" s="8"/>
       <c r="X2" s="8"/>
     </row>
-    <row r="3" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -1221,7 +1221,7 @@
       <c r="W3" s="8"/>
       <c r="X3" s="8"/>
     </row>
-    <row r="4" spans="1:24" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:24" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -1251,7 +1251,7 @@
       <c r="W4" s="9"/>
       <c r="X4" s="9"/>
     </row>
-    <row r="5" spans="1:24" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1277,7 +1277,7 @@
       <c r="W5" s="2"/>
       <c r="X5" s="2"/>
     </row>
-    <row r="6" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
         <v>6</v>
       </c>
@@ -1305,7 +1305,7 @@
       <c r="W6" s="10"/>
       <c r="X6" s="10"/>
     </row>
-    <row r="7" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>7</v>
       </c>
@@ -1333,7 +1333,7 @@
       <c r="W7" s="11"/>
       <c r="X7" s="11"/>
     </row>
-    <row r="8" spans="1:24" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -1359,7 +1359,7 @@
       <c r="W8" s="2"/>
       <c r="X8" s="2"/>
     </row>
-    <row r="9" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="12" t="s">
         <v>8</v>
@@ -1387,7 +1387,7 @@
       <c r="W9" s="2"/>
       <c r="X9" s="2"/>
     </row>
-    <row r="10" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="B10" s="13" t="s">
         <v>9</v>
@@ -1421,7 +1421,7 @@
       <c r="W10" s="12"/>
       <c r="X10" s="12"/>
     </row>
-    <row r="11" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="13" t="s">
         <v>13</v>
@@ -1455,7 +1455,7 @@
       <c r="W11" s="13"/>
       <c r="X11" s="13"/>
     </row>
-    <row r="12" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="13" t="s">
         <v>17</v>
@@ -1485,7 +1485,7 @@
       <c r="W12" s="13"/>
       <c r="X12" s="13"/>
     </row>
-    <row r="13" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="13" t="s">
         <v>19</v>
@@ -1523,7 +1523,7 @@
       <c r="W13" s="13"/>
       <c r="X13" s="13"/>
     </row>
-    <row r="14" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="13" t="s">
         <v>25</v>
@@ -1553,7 +1553,7 @@
       <c r="W14" s="12"/>
       <c r="X14" s="12"/>
     </row>
-    <row r="15" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="13" t="s">
         <v>26</v>
@@ -1583,7 +1583,7 @@
       <c r="W15" s="13"/>
       <c r="X15" s="13"/>
     </row>
-    <row r="16" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
       <c r="B16" s="13" t="s">
         <v>27</v>
@@ -1617,7 +1617,7 @@
       <c r="W16" s="14"/>
       <c r="X16" s="14"/>
     </row>
-    <row r="17" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="12" t="s">
         <v>31</v>
@@ -1645,7 +1645,7 @@
       <c r="W17" s="2"/>
       <c r="X17" s="2"/>
     </row>
-    <row r="18" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="13" t="s">
         <v>9</v>
@@ -1679,7 +1679,7 @@
       <c r="W18" s="12"/>
       <c r="X18" s="12"/>
     </row>
-    <row r="19" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="13" t="s">
         <v>15</v>
@@ -1713,7 +1713,7 @@
       <c r="W19" s="13"/>
       <c r="X19" s="13"/>
     </row>
-    <row r="20" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
       <c r="B20" s="13" t="s">
         <v>17</v>
@@ -1743,7 +1743,7 @@
       <c r="W20" s="13"/>
       <c r="X20" s="13"/>
     </row>
-    <row r="21" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="13" t="s">
         <v>38</v>
@@ -1779,7 +1779,7 @@
       <c r="W21" s="13"/>
       <c r="X21" s="13"/>
     </row>
-    <row r="22" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
       <c r="B22" s="13" t="s">
         <v>27</v>
@@ -1807,7 +1807,7 @@
       <c r="W22" s="2"/>
       <c r="X22" s="2"/>
     </row>
-    <row r="23" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
       <c r="B23" s="14" t="s">
         <v>40</v>
@@ -1835,7 +1835,7 @@
       <c r="W23" s="14"/>
       <c r="X23" s="14"/>
     </row>
-    <row r="24" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
       <c r="B24" s="12" t="s">
         <v>41</v>
@@ -1863,7 +1863,7 @@
       <c r="W24" s="12"/>
       <c r="X24" s="12"/>
     </row>
-    <row r="25" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
       <c r="B25" s="13" t="s">
         <v>42</v>
@@ -1893,7 +1893,7 @@
       <c r="W25" s="13"/>
       <c r="X25" s="13"/>
     </row>
-    <row r="26" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
       <c r="B26" s="13" t="s">
         <v>44</v>
@@ -1921,10 +1921,10 @@
       <c r="W26" s="13"/>
       <c r="X26" s="2"/>
     </row>
-    <row r="27" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
       <c r="B27" s="15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C27" s="13"/>
       <c r="D27" s="13"/>
@@ -1949,7 +1949,7 @@
       <c r="W27" s="13"/>
       <c r="X27" s="13"/>
     </row>
-    <row r="28" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -1977,7 +1977,7 @@
       <c r="W28" s="13"/>
       <c r="X28" s="13"/>
     </row>
-    <row r="29" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
       <c r="B29" s="13" t="s">
         <v>46</v>
@@ -2007,7 +2007,7 @@
       <c r="W29" s="13"/>
       <c r="X29" s="13"/>
     </row>
-    <row r="30" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2"/>
       <c r="B30" s="13" t="s">
         <v>48</v>
@@ -2037,7 +2037,7 @@
       <c r="W30" s="13"/>
       <c r="X30" s="13"/>
     </row>
-    <row r="31" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
       <c r="B31" s="13" t="s">
         <v>50</v>
@@ -2065,7 +2065,7 @@
       <c r="W31" s="13"/>
       <c r="X31" s="13"/>
     </row>
-    <row r="32" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2"/>
       <c r="B32" s="12" t="s">
         <v>51</v>
@@ -2093,7 +2093,7 @@
       <c r="W32" s="12"/>
       <c r="X32" s="12"/>
     </row>
-    <row r="33" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
       <c r="B33" s="13" t="s">
         <v>52</v>
@@ -2121,7 +2121,7 @@
       <c r="W33" s="13"/>
       <c r="X33" s="13"/>
     </row>
-    <row r="34" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2"/>
       <c r="B34" s="13" t="s">
         <v>53</v>
@@ -2149,7 +2149,7 @@
       <c r="W34" s="13"/>
       <c r="X34" s="13"/>
     </row>
-    <row r="35" spans="1:24" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:24" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
       <c r="B35" s="13" t="s">
         <v>54</v>
@@ -2177,7 +2177,7 @@
       <c r="W35" s="13"/>
       <c r="X35" s="13"/>
     </row>
-    <row r="36" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -2203,7 +2203,7 @@
       <c r="W36" s="2"/>
       <c r="X36" s="2"/>
     </row>
-    <row r="37" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
       <c r="B37" s="12" t="s">
         <v>55</v>
@@ -2231,7 +2231,7 @@
       <c r="W37" s="12"/>
       <c r="X37" s="12"/>
     </row>
-    <row r="38" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
       <c r="B38" s="16" t="s">
         <v>56</v>
@@ -2259,7 +2259,7 @@
       <c r="W38" s="16"/>
       <c r="X38" s="16"/>
     </row>
-    <row r="39" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2"/>
       <c r="B39" s="12" t="s">
         <v>57</v>
@@ -2289,7 +2289,7 @@
       <c r="W39" s="17"/>
       <c r="X39" s="17"/>
     </row>
-    <row r="40" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2"/>
       <c r="B40" s="18" t="s">
         <v>59</v>
@@ -2319,7 +2319,7 @@
       <c r="W40" s="19"/>
       <c r="X40" s="19"/>
     </row>
-    <row r="41" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
@@ -2345,7 +2345,7 @@
       <c r="W41" s="2"/>
       <c r="X41" s="2"/>
     </row>
-    <row r="42" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2"/>
       <c r="B42" s="12" t="s">
         <v>60</v>
@@ -2375,7 +2375,7 @@
       <c r="W42" s="13"/>
       <c r="X42" s="13"/>
     </row>
-    <row r="43" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2"/>
       <c r="B43" s="13" t="s">
         <v>62</v>
@@ -2403,7 +2403,7 @@
       <c r="W43" s="13"/>
       <c r="X43" s="13"/>
     </row>
-    <row r="44" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2"/>
       <c r="B44" s="13" t="s">
         <v>63</v>
@@ -2431,7 +2431,7 @@
       <c r="W44" s="13"/>
       <c r="X44" s="13"/>
     </row>
-    <row r="45" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2"/>
       <c r="B45" s="12" t="s">
         <v>64</v>
@@ -2459,7 +2459,7 @@
       <c r="W45" s="2"/>
       <c r="X45" s="2"/>
     </row>
-    <row r="46" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2"/>
       <c r="B46" s="12" t="s">
         <v>65</v>
@@ -2487,7 +2487,7 @@
       <c r="W46" s="12"/>
       <c r="X46" s="12"/>
     </row>
-    <row r="47" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2"/>
       <c r="B47" s="13" t="s">
         <v>66</v>
@@ -2515,7 +2515,7 @@
       <c r="W47" s="13"/>
       <c r="X47" s="13"/>
     </row>
-    <row r="48" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2"/>
       <c r="B48" s="20" t="s">
         <v>67</v>
@@ -2543,7 +2543,7 @@
       <c r="W48" s="13"/>
       <c r="X48" s="13"/>
     </row>
-    <row r="49" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2"/>
       <c r="B49" s="12" t="s">
         <v>68</v>
@@ -2573,7 +2573,7 @@
       <c r="W49" s="13"/>
       <c r="X49" s="13"/>
     </row>
-    <row r="50" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2"/>
       <c r="B50" s="13" t="s">
         <v>70</v>
@@ -2601,7 +2601,7 @@
       <c r="W50" s="13"/>
       <c r="X50" s="2"/>
     </row>
-    <row r="51" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2"/>
       <c r="B51" s="12" t="s">
         <v>71</v>
@@ -2629,7 +2629,7 @@
       <c r="W51" s="2"/>
       <c r="X51" s="2"/>
     </row>
-    <row r="52" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2"/>
       <c r="B52" s="13" t="s">
         <v>72</v>
@@ -2657,7 +2657,7 @@
       <c r="W52" s="13"/>
       <c r="X52" s="13"/>
     </row>
-    <row r="53" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2"/>
       <c r="B53" s="13" t="s">
         <v>73</v>
@@ -2685,7 +2685,7 @@
       <c r="W53" s="13"/>
       <c r="X53" s="13"/>
     </row>
-    <row r="54" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2"/>
       <c r="B54" s="12" t="s">
         <v>74</v>
@@ -2713,7 +2713,7 @@
       <c r="W54" s="2"/>
       <c r="X54" s="2"/>
     </row>
-    <row r="55" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2"/>
       <c r="B55" s="13" t="s">
         <v>75</v>
@@ -2741,7 +2741,7 @@
       <c r="W55" s="13"/>
       <c r="X55" s="13"/>
     </row>
-    <row r="56" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2"/>
       <c r="B56" s="13" t="s">
         <v>76</v>
@@ -2769,7 +2769,7 @@
       <c r="W56" s="13"/>
       <c r="X56" s="13"/>
     </row>
-    <row r="57" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2"/>
       <c r="B57" s="13" t="s">
         <v>77</v>
@@ -2797,7 +2797,7 @@
       <c r="W57" s="13"/>
       <c r="X57" s="13"/>
     </row>
-    <row r="58" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2"/>
       <c r="B58" s="12" t="s">
         <v>78</v>
@@ -2825,7 +2825,7 @@
       <c r="W58" s="12"/>
       <c r="X58" s="12"/>
     </row>
-    <row r="59" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2"/>
       <c r="B59" s="13" t="s">
         <v>79</v>
@@ -2853,7 +2853,7 @@
       <c r="W59" s="13"/>
       <c r="X59" s="13"/>
     </row>
-    <row r="60" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2"/>
       <c r="B60" s="13" t="s">
         <v>80</v>
@@ -2881,7 +2881,7 @@
       <c r="W60" s="13"/>
       <c r="X60" s="13"/>
     </row>
-    <row r="61" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2"/>
       <c r="B61" s="13" t="s">
         <v>81</v>
@@ -2909,7 +2909,7 @@
       <c r="W61" s="13"/>
       <c r="X61" s="13"/>
     </row>
-    <row r="62" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2"/>
       <c r="B62" s="13" t="s">
         <v>82</v>
@@ -2937,7 +2937,7 @@
       <c r="W62" s="13"/>
       <c r="X62" s="13"/>
     </row>
-    <row r="63" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2"/>
       <c r="B63" s="12" t="s">
         <v>83</v>
@@ -2965,7 +2965,7 @@
       <c r="W63" s="12"/>
       <c r="X63" s="12"/>
     </row>
-    <row r="64" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2"/>
       <c r="B64" s="13" t="s">
         <v>84</v>
@@ -2993,7 +2993,7 @@
       <c r="W64" s="13"/>
       <c r="X64" s="13"/>
     </row>
-    <row r="65" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2"/>
       <c r="B65" s="21" t="s">
         <v>85</v>
@@ -3021,7 +3021,7 @@
       <c r="W65" s="22"/>
       <c r="X65" s="22"/>
     </row>
-    <row r="66" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2"/>
       <c r="B66" s="22" t="s">
         <v>86</v>
@@ -3049,7 +3049,7 @@
       <c r="W66" s="22"/>
       <c r="X66" s="22"/>
     </row>
-    <row r="67" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2"/>
       <c r="B67" s="23" t="s">
         <v>142</v>
@@ -3077,7 +3077,7 @@
       <c r="W67" s="23"/>
       <c r="X67" s="23"/>
     </row>
-    <row r="68" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2"/>
       <c r="B68" s="12" t="s">
         <v>87</v>
@@ -3105,7 +3105,7 @@
       <c r="W68" s="12"/>
       <c r="X68" s="12"/>
     </row>
-    <row r="69" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2"/>
       <c r="B69" s="13" t="s">
         <v>88</v>
@@ -3133,7 +3133,7 @@
       <c r="W69" s="13"/>
       <c r="X69" s="13"/>
     </row>
-    <row r="70" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2"/>
       <c r="B70" s="12" t="s">
         <v>143</v>
@@ -3161,7 +3161,7 @@
       <c r="W70" s="12"/>
       <c r="X70" s="12"/>
     </row>
-    <row r="71" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2"/>
       <c r="B71" s="12" t="s">
         <v>89</v>
@@ -3189,7 +3189,7 @@
       <c r="W71" s="12"/>
       <c r="X71" s="12"/>
     </row>
-    <row r="72" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2"/>
       <c r="B72" s="13" t="s">
         <v>90</v>
@@ -3217,7 +3217,7 @@
       <c r="W72" s="13"/>
       <c r="X72" s="13"/>
     </row>
-    <row r="73" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2"/>
       <c r="B73" s="13" t="s">
         <v>91</v>
@@ -3245,7 +3245,7 @@
       <c r="W73" s="13"/>
       <c r="X73" s="13"/>
     </row>
-    <row r="74" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2"/>
       <c r="B74" s="13" t="s">
         <v>92</v>
@@ -3273,7 +3273,7 @@
       <c r="W74" s="13"/>
       <c r="X74" s="13"/>
     </row>
-    <row r="75" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2"/>
       <c r="B75" s="13" t="s">
         <v>93</v>
@@ -3301,7 +3301,7 @@
       <c r="W75" s="13"/>
       <c r="X75" s="2"/>
     </row>
-    <row r="76" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2"/>
       <c r="B76" s="13" t="s">
         <v>94</v>
@@ -3329,7 +3329,7 @@
       <c r="W76" s="13"/>
       <c r="X76" s="13"/>
     </row>
-    <row r="77" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2"/>
       <c r="B77" s="13" t="s">
         <v>95</v>
@@ -3357,7 +3357,7 @@
       <c r="W77" s="13"/>
       <c r="X77" s="13"/>
     </row>
-    <row r="78" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2"/>
       <c r="B78" s="13" t="s">
         <v>96</v>
@@ -3385,7 +3385,7 @@
       <c r="W78" s="13"/>
       <c r="X78" s="13"/>
     </row>
-    <row r="79" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2"/>
       <c r="B79" s="13" t="s">
         <v>97</v>
@@ -3413,7 +3413,7 @@
       <c r="W79" s="13"/>
       <c r="X79" s="13"/>
     </row>
-    <row r="80" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2"/>
       <c r="B80" s="13" t="s">
         <v>98</v>
@@ -3441,7 +3441,7 @@
       <c r="W80" s="13"/>
       <c r="X80" s="13"/>
     </row>
-    <row r="81" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2"/>
       <c r="B81" s="16" t="s">
         <v>99</v>
@@ -3469,7 +3469,7 @@
       <c r="W81" s="16"/>
       <c r="X81" s="16"/>
     </row>
-    <row r="82" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2"/>
       <c r="B82" s="13" t="s">
         <v>100</v>
@@ -3497,7 +3497,7 @@
       <c r="W82" s="13"/>
       <c r="X82" s="13"/>
     </row>
-    <row r="83" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2"/>
       <c r="B83" s="13" t="s">
         <v>101</v>
@@ -3525,7 +3525,7 @@
       <c r="W83" s="13"/>
       <c r="X83" s="13"/>
     </row>
-    <row r="84" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2"/>
       <c r="B84" s="13" t="s">
         <v>102</v>
@@ -3553,7 +3553,7 @@
       <c r="W84" s="13"/>
       <c r="X84" s="13"/>
     </row>
-    <row r="85" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2"/>
       <c r="B85" s="13" t="s">
         <v>103</v>
@@ -3581,7 +3581,7 @@
       <c r="W85" s="13"/>
       <c r="X85" s="13"/>
     </row>
-    <row r="86" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2"/>
       <c r="B86" s="13" t="s">
         <v>104</v>
@@ -3609,7 +3609,7 @@
       <c r="W86" s="13"/>
       <c r="X86" s="13"/>
     </row>
-    <row r="87" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2"/>
       <c r="B87" s="13" t="s">
         <v>105</v>
@@ -3637,7 +3637,7 @@
       <c r="W87" s="13"/>
       <c r="X87" s="13"/>
     </row>
-    <row r="88" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2"/>
       <c r="B88" s="13" t="s">
         <v>106</v>
@@ -3665,7 +3665,7 @@
       <c r="W88" s="13"/>
       <c r="X88" s="13"/>
     </row>
-    <row r="89" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2"/>
       <c r="B89" s="13" t="s">
         <v>107</v>
@@ -3693,7 +3693,7 @@
       <c r="W89" s="13"/>
       <c r="X89" s="13"/>
     </row>
-    <row r="90" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2"/>
       <c r="B90" s="13" t="s">
         <v>108</v>
@@ -3721,7 +3721,7 @@
       <c r="W90" s="13"/>
       <c r="X90" s="13"/>
     </row>
-    <row r="91" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2"/>
       <c r="B91" s="13" t="s">
         <v>109</v>
@@ -3749,7 +3749,7 @@
       <c r="W91" s="13"/>
       <c r="X91" s="13"/>
     </row>
-    <row r="92" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2"/>
       <c r="B92" s="13" t="s">
         <v>110</v>
@@ -3777,7 +3777,7 @@
       <c r="W92" s="13"/>
       <c r="X92" s="13"/>
     </row>
-    <row r="93" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2"/>
       <c r="B93" s="13" t="s">
         <v>111</v>
@@ -3805,7 +3805,7 @@
       <c r="W93" s="13"/>
       <c r="X93" s="13"/>
     </row>
-    <row r="94" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2"/>
       <c r="B94" s="13" t="s">
         <v>112</v>
@@ -3833,7 +3833,7 @@
       <c r="W94" s="13"/>
       <c r="X94" s="13"/>
     </row>
-    <row r="95" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2"/>
       <c r="B95" s="13" t="s">
         <v>113</v>
@@ -3861,7 +3861,7 @@
       <c r="W95" s="13"/>
       <c r="X95" s="13"/>
     </row>
-    <row r="96" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2"/>
       <c r="B96" s="13" t="s">
         <v>114</v>
@@ -3889,7 +3889,7 @@
       <c r="W96" s="13"/>
       <c r="X96" s="13"/>
     </row>
-    <row r="97" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2"/>
       <c r="B97" s="13" t="s">
         <v>115</v>
@@ -3917,7 +3917,7 @@
       <c r="W97" s="13"/>
       <c r="X97" s="13"/>
     </row>
-    <row r="98" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2"/>
       <c r="B98" s="13" t="s">
         <v>116</v>
@@ -3945,7 +3945,7 @@
       <c r="W98" s="13"/>
       <c r="X98" s="13"/>
     </row>
-    <row r="99" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2"/>
       <c r="B99" s="2"/>
       <c r="C99" s="2"/>
@@ -3971,7 +3971,7 @@
       <c r="W99" s="2"/>
       <c r="X99" s="2"/>
     </row>
-    <row r="100" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2"/>
       <c r="B100" s="12" t="s">
         <v>117</v>
@@ -3999,7 +3999,7 @@
       <c r="W100" s="12"/>
       <c r="X100" s="12"/>
     </row>
-    <row r="101" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2"/>
       <c r="B101" s="12" t="s">
         <v>118</v>
@@ -4027,7 +4027,7 @@
       <c r="W101" s="12"/>
       <c r="X101" s="12"/>
     </row>
-    <row r="102" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2"/>
       <c r="B102" s="13" t="s">
         <v>119</v>
@@ -4055,7 +4055,7 @@
       <c r="W102" s="13"/>
       <c r="X102" s="13"/>
     </row>
-    <row r="103" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2"/>
       <c r="B103" s="13" t="s">
         <v>120</v>
@@ -4083,7 +4083,7 @@
       <c r="W103" s="13"/>
       <c r="X103" s="13"/>
     </row>
-    <row r="104" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2"/>
       <c r="B104" s="13" t="s">
         <v>121</v>
@@ -4111,7 +4111,7 @@
       <c r="W104" s="13"/>
       <c r="X104" s="13"/>
     </row>
-    <row r="105" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2"/>
       <c r="B105" s="13" t="s">
         <v>122</v>
@@ -4139,7 +4139,7 @@
       <c r="W105" s="13"/>
       <c r="X105" s="13"/>
     </row>
-    <row r="106" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2"/>
       <c r="B106" s="13" t="s">
         <v>123</v>
@@ -4167,7 +4167,7 @@
       <c r="W106" s="13"/>
       <c r="X106" s="13"/>
     </row>
-    <row r="107" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="2"/>
       <c r="B107" s="12" t="s">
         <v>124</v>
@@ -4195,7 +4195,7 @@
       <c r="W107" s="12"/>
       <c r="X107" s="12"/>
     </row>
-    <row r="108" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2"/>
       <c r="B108" s="13" t="s">
         <v>125</v>
@@ -4223,7 +4223,7 @@
       <c r="W108" s="13"/>
       <c r="X108" s="13"/>
     </row>
-    <row r="109" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2"/>
       <c r="B109" s="13" t="s">
         <v>126</v>
@@ -4251,7 +4251,7 @@
       <c r="W109" s="13"/>
       <c r="X109" s="13"/>
     </row>
-    <row r="110" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2"/>
       <c r="B110" s="13" t="s">
         <v>127</v>
@@ -4279,7 +4279,7 @@
       <c r="W110" s="13"/>
       <c r="X110" s="13"/>
     </row>
-    <row r="111" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="2"/>
       <c r="B111" s="13" t="s">
         <v>128</v>
@@ -4307,7 +4307,7 @@
       <c r="W111" s="13"/>
       <c r="X111" s="13"/>
     </row>
-    <row r="112" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="2"/>
       <c r="B112" s="12" t="s">
         <v>129</v>
@@ -4335,7 +4335,7 @@
       <c r="W112" s="12"/>
       <c r="X112" s="12"/>
     </row>
-    <row r="113" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="2"/>
       <c r="B113" s="13" t="s">
         <v>130</v>
@@ -4363,7 +4363,7 @@
       <c r="W113" s="13"/>
       <c r="X113" s="13"/>
     </row>
-    <row r="114" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="2"/>
       <c r="B114" s="13" t="s">
         <v>131</v>
@@ -4391,7 +4391,7 @@
       <c r="W114" s="13"/>
       <c r="X114" s="13"/>
     </row>
-    <row r="115" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="2"/>
       <c r="B115" s="13" t="s">
         <v>132</v>
@@ -4419,7 +4419,7 @@
       <c r="W115" s="13"/>
       <c r="X115" s="13"/>
     </row>
-    <row r="116" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="2"/>
       <c r="B116" s="13" t="s">
         <v>133</v>
@@ -4447,7 +4447,7 @@
       <c r="W116" s="13"/>
       <c r="X116" s="13"/>
     </row>
-    <row r="117" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="2"/>
       <c r="B117" s="13" t="s">
         <v>134</v>
@@ -4475,7 +4475,7 @@
       <c r="W117" s="13"/>
       <c r="X117" s="13"/>
     </row>
-    <row r="118" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="2"/>
       <c r="B118" s="24" t="s">
         <v>135</v>
@@ -4505,7 +4505,7 @@
       <c r="W118" s="24"/>
       <c r="X118" s="24"/>
     </row>
-    <row r="119" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="2"/>
       <c r="B119" s="9" t="s">
         <v>137</v>
@@ -4533,7 +4533,7 @@
       <c r="W119" s="9"/>
       <c r="X119" s="9"/>
     </row>
-    <row r="120" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2"/>
       <c r="B120" s="2"/>
       <c r="C120" s="2"/>
@@ -4559,7 +4559,7 @@
       <c r="W120" s="2"/>
       <c r="X120" s="2"/>
     </row>
-    <row r="121" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="2"/>
       <c r="B121" s="2"/>
       <c r="C121" s="2"/>
@@ -4585,7 +4585,7 @@
       <c r="W121" s="2"/>
       <c r="X121" s="2"/>
     </row>
-    <row r="122" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="2"/>
       <c r="B122" s="2"/>
       <c r="C122" s="2"/>
@@ -4611,7 +4611,7 @@
       <c r="W122" s="2"/>
       <c r="X122" s="2"/>
     </row>
-    <row r="123" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="2"/>
       <c r="B123" s="2"/>
       <c r="C123" s="2"/>
@@ -4637,7 +4637,7 @@
       <c r="W123" s="2"/>
       <c r="X123" s="2"/>
     </row>
-    <row r="124" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="2"/>
       <c r="B124" s="2"/>
       <c r="C124" s="2"/>
@@ -4667,7 +4667,7 @@
       <c r="W124" s="13"/>
       <c r="X124" s="13"/>
     </row>
-    <row r="125" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="2"/>
       <c r="B125" s="2"/>
       <c r="C125" s="2"/>
@@ -4695,7 +4695,7 @@
       <c r="W125" s="13"/>
       <c r="X125" s="2"/>
     </row>
-    <row r="126" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="2"/>
       <c r="B126" s="2"/>
       <c r="C126" s="2"/>
@@ -4725,7 +4725,7 @@
       <c r="W126" s="2"/>
       <c r="X126" s="2"/>
     </row>
-    <row r="127" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B127" s="2"/>
       <c r="C127" s="2"/>
       <c r="D127" s="2"/>
